--- a/InputData/bldgs/SoBRCbIC/Shr of Bldg Retrofitting Costs by ISIC Code.xlsx
+++ b/InputData/bldgs/SoBRCbIC/Shr of Bldg Retrofitting Costs by ISIC Code.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\.claude\worktrees\retrofit-isic-split\InputData\bldgs\SoBRCbIC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00A1607B-485C-4F41-8217-525137EB6038}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11FF655D-55BE-4444-9815-051229B28EE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1314" uniqueCount="447">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1317" uniqueCount="450">
   <si>
     <t>SoBRCbIC Shr of Bldg Retrofitting Costs by ISIC Code</t>
   </si>
@@ -214,7 +214,7 @@
     <t>Commercial</t>
   </si>
   <si>
-    <t>For each measure BRESaC counts, PNNL gives an equipment cost and an installation cost in five climate zones. Each climate zone is weighted by its share of BRESaC's average cost per BTU (floorspace times cost per BTU), and within a zone each measure by its share of that zone's cost. Commercial heating and cooling get the same split, because the measures serve both.</t>
+    <t>For each measure BRESaC counts, PNNL gives an equipment cost and an installation cost in five climate zones. Each climate zone is weighted by its share of BRESaC's average cost per BTU (floorspace times cost per BTU), and within a zone each measure by its share of that zone's cost. Commercial heating and cooling get the same split, because the measures serve both. PNNL prices four of the measures (HA13, HA14, HA15 and HW15) as if each one had to upgrade the building's zone controls from pneumatic to digital. A building only does that once, so it is counted once, in HA13, as BRESaC does; the upgrade's cost is HA14 minus HA12, two versions of the same measure with and without it.</t>
   </si>
   <si>
     <t>What is not covered</t>
@@ -995,7 +995,7 @@
     <t>HW12 Add a VFD to One Chiller</t>
   </si>
   <si>
-    <t>HW15 Replace Boiler Burners with Modulating Burners</t>
+    <t>HW15 Replace Boilers and Change Heating Plant Pumping System to Variable Flow Primary</t>
   </si>
   <si>
     <t>A. Residential: how much of retrofit spending is envelope work</t>
@@ -1147,6 +1147,19 @@
     <t>Total cost of the counted measures in one building ($)</t>
   </si>
   <si>
+    <t>Digital zone control upgrade
+equipment ($)
+HA14 minus HA12</t>
+  </si>
+  <si>
+    <t>Digital zone control upgrade
+installation ($)
+HA14 minus HA12</t>
+  </si>
+  <si>
+    <t>HA13, HA14, HA15 and HW15 each include the full upgrade from pneumatic to digital zone controls. It is counted once, in HA13; the other three have it subtracted.</t>
+  </si>
+  <si>
     <t>BRESaC measure</t>
   </si>
   <si>
@@ -1276,7 +1289,7 @@
     <t>VFD for one chiller compressor</t>
   </si>
   <si>
-    <t>Modulating boiler burners</t>
+    <t>Condensing boilers and pumps (DDC upgrade counted under HA13)</t>
   </si>
   <si>
     <t>Total cost of counted measures in one building ($)</t>
@@ -2096,7 +2109,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="44" spans="1:2" ht="60" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
         <v>55</v>
       </c>
@@ -5287,19 +5300,19 @@
       </c>
       <c r="V2">
         <f>INDEX(Calcs!$F$58:$F$109,MATCH(V$1,Calcs!$A$58:$A$109,0))</f>
-        <v>0</v>
+        <v>6.2652119642991694E-2</v>
       </c>
       <c r="W2">
         <f>INDEX(Calcs!$F$58:$F$109,MATCH(W$1,Calcs!$A$58:$A$109,0))</f>
-        <v>0.15189975434567671</v>
+        <v>8.2476824567215584E-2</v>
       </c>
       <c r="X2">
         <f>INDEX(Calcs!$F$58:$F$109,MATCH(X$1,Calcs!$A$58:$A$109,0))</f>
-        <v>2.4713665761134956E-2</v>
+        <v>3.5622900571994909E-2</v>
       </c>
       <c r="Y2">
         <f>INDEX(Calcs!$F$58:$F$109,MATCH(Y$1,Calcs!$A$58:$A$109,0))</f>
-        <v>6.7850177477708955E-3</v>
+        <v>7.446325552416035E-3</v>
       </c>
       <c r="Z2">
         <f>INDEX(Calcs!$F$58:$F$109,MATCH(Z$1,Calcs!$A$58:$A$109,0))</f>
@@ -5331,15 +5344,15 @@
       </c>
       <c r="AG2">
         <f>INDEX(Calcs!$F$58:$F$109,MATCH(AG$1,Calcs!$A$58:$A$109,0))</f>
-        <v>0.75594162438251167</v>
+        <v>0.70452348304815571</v>
       </c>
       <c r="AH2">
         <f>INDEX(Calcs!$F$58:$F$109,MATCH(AH$1,Calcs!$A$58:$A$109,0))</f>
-        <v>5.5813720451677588E-2</v>
+        <v>0.10240893888644097</v>
       </c>
       <c r="AI2">
         <f>INDEX(Calcs!$F$58:$F$109,MATCH(AI$1,Calcs!$A$58:$A$109,0))</f>
-        <v>4.8462173112280597E-3</v>
+        <v>4.8694077307852874E-3</v>
       </c>
       <c r="AJ2">
         <f>INDEX(Calcs!$F$58:$F$109,MATCH(AJ$1,Calcs!$A$58:$A$109,0))</f>
@@ -5500,19 +5513,19 @@
       </c>
       <c r="V3">
         <f>INDEX(Calcs!$G$58:$G$109,MATCH(V$1,Calcs!$A$58:$A$109,0))</f>
-        <v>0</v>
+        <v>6.2652119642991694E-2</v>
       </c>
       <c r="W3">
         <f>INDEX(Calcs!$G$58:$G$109,MATCH(W$1,Calcs!$A$58:$A$109,0))</f>
-        <v>0.15189975434567671</v>
+        <v>8.2476824567215584E-2</v>
       </c>
       <c r="X3">
         <f>INDEX(Calcs!$G$58:$G$109,MATCH(X$1,Calcs!$A$58:$A$109,0))</f>
-        <v>2.4713665761134956E-2</v>
+        <v>3.5622900571994909E-2</v>
       </c>
       <c r="Y3">
         <f>INDEX(Calcs!$G$58:$G$109,MATCH(Y$1,Calcs!$A$58:$A$109,0))</f>
-        <v>6.7850177477708955E-3</v>
+        <v>7.446325552416035E-3</v>
       </c>
       <c r="Z3">
         <f>INDEX(Calcs!$G$58:$G$109,MATCH(Z$1,Calcs!$A$58:$A$109,0))</f>
@@ -5544,15 +5557,15 @@
       </c>
       <c r="AG3">
         <f>INDEX(Calcs!$G$58:$G$109,MATCH(AG$1,Calcs!$A$58:$A$109,0))</f>
-        <v>0.75594162438251167</v>
+        <v>0.70452348304815571</v>
       </c>
       <c r="AH3">
         <f>INDEX(Calcs!$G$58:$G$109,MATCH(AH$1,Calcs!$A$58:$A$109,0))</f>
-        <v>5.5813720451677588E-2</v>
+        <v>0.10240893888644097</v>
       </c>
       <c r="AI3">
         <f>INDEX(Calcs!$G$58:$G$109,MATCH(AI$1,Calcs!$A$58:$A$109,0))</f>
-        <v>4.8462173112280597E-3</v>
+        <v>4.8694077307852874E-3</v>
       </c>
       <c r="AJ3">
         <f>INDEX(Calcs!$G$58:$G$109,MATCH(AJ$1,Calcs!$A$58:$A$109,0))</f>
@@ -14816,7 +14829,7 @@
         <v>0.40566317524959927</v>
       </c>
       <c r="C37">
-        <v>1.650456547179108E-4</v>
+        <v>9.1827574525745243E-5</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -14827,7 +14840,7 @@
         <v>6.1563024941687562E-2</v>
       </c>
       <c r="C38">
-        <v>2.6529571746559228E-4</v>
+        <v>1.959678809919428E-4</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -14838,7 +14851,7 @@
         <v>3.7672564038317383E-2</v>
       </c>
       <c r="C39">
-        <v>2.00824058530716E-4</v>
+        <v>1.9606404513407841E-4</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -14849,7 +14862,7 @@
         <v>0.45140543049506737</v>
       </c>
       <c r="C40">
-        <v>3.021342683414829E-4</v>
+        <v>2.1417364549585339E-4</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -14860,7 +14873,7 @@
         <v>4.3695805275328507E-2</v>
       </c>
       <c r="C41">
-        <v>3.1782992160278752E-4</v>
+        <v>2.152723271593618E-4</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -16306,6 +16319,12 @@
       <c r="E31" s="6" t="s">
         <v>362</v>
       </c>
+      <c r="F31" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="G31" s="6" t="s">
+        <v>364</v>
+      </c>
     </row>
     <row r="32" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
@@ -16317,15 +16336,23 @@
       </c>
       <c r="C32" s="15">
         <f>'EPS Inputs'!C37</f>
-        <v>1.650456547179108E-4</v>
+        <v>9.1827574525745243E-5</v>
       </c>
       <c r="D32" s="13">
         <f>B32*C32/SUMPRODUCT($B$32:$B$36,$C$32:$C$36)</f>
-        <v>0.27767041869010334</v>
+        <v>0.22883272058703505</v>
       </c>
       <c r="E32" s="7">
         <f>G51</f>
-        <v>857499</v>
+        <v>477093</v>
+      </c>
+      <c r="F32" s="7">
+        <f>SUMIFS('PNNL Office Measures'!$E$5:$E$69,'PNNL Office Measures'!$A$5:$A$69,"HA14",'PNNL Office Measures'!$D$5:$D$69,$A32)-SUMIFS('PNNL Office Measures'!$E$5:$E$69,'PNNL Office Measures'!$A$5:$A$69,"HA12",'PNNL Office Measures'!$D$5:$D$69,$A32)</f>
+        <v>61907</v>
+      </c>
+      <c r="G32" s="7">
+        <f>SUMIFS('PNNL Office Measures'!$F$5:$F$69,'PNNL Office Measures'!$A$5:$A$69,"HA14",'PNNL Office Measures'!$D$5:$D$69,$A32)-SUMIFS('PNNL Office Measures'!$F$5:$F$69,'PNNL Office Measures'!$A$5:$A$69,"HA12",'PNNL Office Measures'!$D$5:$D$69,$A32)</f>
+        <v>128296</v>
       </c>
     </row>
     <row r="33" spans="1:28" x14ac:dyDescent="0.25">
@@ -16338,15 +16365,23 @@
       </c>
       <c r="C33" s="15">
         <f>'EPS Inputs'!C38</f>
-        <v>2.6529571746559228E-4</v>
+        <v>1.959678809919428E-4</v>
       </c>
       <c r="D33" s="13">
         <f>B33*C33/SUMPRODUCT($B$32:$B$36,$C$32:$C$36)</f>
-        <v>6.7734530541031013E-2</v>
+        <v>7.4111272907158104E-2</v>
       </c>
       <c r="E33" s="7">
         <f>J51</f>
-        <v>1383954</v>
+        <v>1000130</v>
+      </c>
+      <c r="F33" s="7">
+        <f>SUMIFS('PNNL Office Measures'!$E$5:$E$69,'PNNL Office Measures'!$A$5:$A$69,"HA14",'PNNL Office Measures'!$D$5:$D$69,$A33)-SUMIFS('PNNL Office Measures'!$E$5:$E$69,'PNNL Office Measures'!$A$5:$A$69,"HA12",'PNNL Office Measures'!$D$5:$D$69,$A33)</f>
+        <v>62463</v>
+      </c>
+      <c r="G33" s="7">
+        <f>SUMIFS('PNNL Office Measures'!$F$5:$F$69,'PNNL Office Measures'!$A$5:$A$69,"HA14",'PNNL Office Measures'!$D$5:$D$69,$A33)-SUMIFS('PNNL Office Measures'!$F$5:$F$69,'PNNL Office Measures'!$A$5:$A$69,"HA12",'PNNL Office Measures'!$D$5:$D$69,$A33)</f>
+        <v>129449</v>
       </c>
     </row>
     <row r="34" spans="1:28" x14ac:dyDescent="0.25">
@@ -16359,15 +16394,23 @@
       </c>
       <c r="C34" s="15">
         <f>'EPS Inputs'!C39</f>
-        <v>2.00824058530716E-4</v>
+        <v>1.9606404513407841E-4</v>
       </c>
       <c r="D34" s="13">
         <f>B34*C34/SUMPRODUCT($B$32:$B$36,$C$32:$C$36)</f>
-        <v>3.1376236805193393E-2</v>
+        <v>4.5373529505810681E-2</v>
       </c>
       <c r="E34" s="7">
         <f>M51</f>
-        <v>1217854</v>
+        <v>1018935</v>
+      </c>
+      <c r="F34" s="7">
+        <f>SUMIFS('PNNL Office Measures'!$E$5:$E$69,'PNNL Office Measures'!$A$5:$A$69,"HA14",'PNNL Office Measures'!$D$5:$D$69,$A34)-SUMIFS('PNNL Office Measures'!$E$5:$E$69,'PNNL Office Measures'!$A$5:$A$69,"HA12",'PNNL Office Measures'!$D$5:$D$69,$A34)</f>
+        <v>64690</v>
+      </c>
+      <c r="G34" s="7">
+        <f>SUMIFS('PNNL Office Measures'!$F$5:$F$69,'PNNL Office Measures'!$A$5:$A$69,"HA14",'PNNL Office Measures'!$D$5:$D$69,$A34)-SUMIFS('PNNL Office Measures'!$F$5:$F$69,'PNNL Office Measures'!$A$5:$A$69,"HA12",'PNNL Office Measures'!$D$5:$D$69,$A34)</f>
+        <v>134064</v>
       </c>
     </row>
     <row r="35" spans="1:28" x14ac:dyDescent="0.25">
@@ -16380,15 +16423,23 @@
       </c>
       <c r="C35" s="15">
         <f>'EPS Inputs'!C40</f>
-        <v>3.021342683414829E-4</v>
+        <v>2.1417364549585339E-4</v>
       </c>
       <c r="D35" s="13">
         <f>B35*C35/SUMPRODUCT($B$32:$B$36,$C$32:$C$36)</f>
-        <v>0.56562253018493103</v>
+        <v>0.59389850677350708</v>
       </c>
       <c r="E35" s="7">
         <f>P51</f>
-        <v>1238255</v>
+        <v>1051099</v>
+      </c>
+      <c r="F35" s="7">
+        <f>SUMIFS('PNNL Office Measures'!$E$5:$E$69,'PNNL Office Measures'!$A$5:$A$69,"HA14",'PNNL Office Measures'!$D$5:$D$69,$A35)-SUMIFS('PNNL Office Measures'!$E$5:$E$69,'PNNL Office Measures'!$A$5:$A$69,"HA12",'PNNL Office Measures'!$D$5:$D$69,$A35)</f>
+        <v>61226</v>
+      </c>
+      <c r="G35" s="7">
+        <f>SUMIFS('PNNL Office Measures'!$F$5:$F$69,'PNNL Office Measures'!$A$5:$A$69,"HA14",'PNNL Office Measures'!$D$5:$D$69,$A35)-SUMIFS('PNNL Office Measures'!$F$5:$F$69,'PNNL Office Measures'!$A$5:$A$69,"HA12",'PNNL Office Measures'!$D$5:$D$69,$A35)</f>
+        <v>126886</v>
       </c>
     </row>
     <row r="36" spans="1:28" x14ac:dyDescent="0.25">
@@ -16401,101 +16452,114 @@
       </c>
       <c r="C36" s="15">
         <f>'EPS Inputs'!C41</f>
-        <v>3.1782992160278752E-4</v>
+        <v>2.152723271593618E-4</v>
       </c>
       <c r="D36" s="13">
         <f>B36*C36/SUMPRODUCT($B$32:$B$36,$C$32:$C$36)</f>
-        <v>5.7596283778741306E-2</v>
+        <v>5.7783970226489186E-2</v>
       </c>
       <c r="E36" s="7">
         <f>S51</f>
-        <v>1225958</v>
+        <v>1056492</v>
+      </c>
+      <c r="F36" s="7">
+        <f>SUMIFS('PNNL Office Measures'!$E$5:$E$69,'PNNL Office Measures'!$A$5:$A$69,"HA14",'PNNL Office Measures'!$D$5:$D$69,$A36)-SUMIFS('PNNL Office Measures'!$E$5:$E$69,'PNNL Office Measures'!$A$5:$A$69,"HA12",'PNNL Office Measures'!$D$5:$D$69,$A36)</f>
+        <v>60979</v>
+      </c>
+      <c r="G36" s="7">
+        <f>SUMIFS('PNNL Office Measures'!$F$5:$F$69,'PNNL Office Measures'!$A$5:$A$69,"HA14",'PNNL Office Measures'!$D$5:$D$69,$A36)-SUMIFS('PNNL Office Measures'!$F$5:$F$69,'PNNL Office Measures'!$A$5:$A$69,"HA12",'PNNL Office Measures'!$D$5:$D$69,$A36)</f>
+        <v>126374</v>
+      </c>
+    </row>
+    <row r="37" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="39" spans="1:28" ht="96" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="K39" s="6" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="L39" s="6" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="M39" s="6" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="N39" s="6" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="O39" s="6" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="P39" s="6" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="Q39" s="6" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="R39" s="6" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="S39" s="6" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="T39" s="6" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="U39" s="6" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="V39" s="6" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="W39" s="6" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="X39" s="6" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="Y39" s="6" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="Z39" s="6" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="AA39" s="6" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="AB39" s="6" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="40" spans="1:28" x14ac:dyDescent="0.25">
@@ -16506,7 +16570,7 @@
         <v>116</v>
       </c>
       <c r="C40" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="D40" t="s">
         <v>353</v>
@@ -16576,11 +16640,11 @@
       </c>
       <c r="U40" s="13">
         <f t="shared" ref="U40:U50" si="0">$D$32*F40*G40/$E$32+$D$33*I40*J40/$E$33+$D$34*L40*M40/$E$34+$D$35*O40*P40/$E$35+$D$36*R40*S40/$E$36</f>
-        <v>7.9945788554424455E-2</v>
+        <v>0.10207593361326465</v>
       </c>
       <c r="V40" s="13">
         <f t="shared" ref="V40:V50" si="1">$D$32*F40*H40/$E$32+$D$33*I40*K40/$E$33+$D$34*L40*N40/$E$34+$D$35*O40*Q40/$E$35+$D$36*R40*T40/$E$36</f>
-        <v>0.1365406317534561</v>
+        <v>0.17434078473781875</v>
       </c>
       <c r="W40" s="13">
         <f>VLOOKUP($D40,Calcs!$A$21:$J$27,8,FALSE)</f>
@@ -16596,7 +16660,7 @@
       </c>
       <c r="Z40" s="13">
         <f t="shared" ref="Z40:Z50" si="2">U40*W40</f>
-        <v>7.9945788554424455E-2</v>
+        <v>0.10207593361326465</v>
       </c>
       <c r="AA40" s="13">
         <f t="shared" ref="AA40:AA50" si="3">U40*Y40</f>
@@ -16615,7 +16679,7 @@
         <v>125</v>
       </c>
       <c r="C41" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="D41" t="s">
         <v>345</v>
@@ -16685,11 +16749,11 @@
       </c>
       <c r="U41" s="13">
         <f t="shared" si="0"/>
-        <v>5.9727962067220614E-2</v>
+        <v>8.0706420718736266E-2</v>
       </c>
       <c r="V41" s="13">
         <f t="shared" si="1"/>
-        <v>0.13230684822690952</v>
+        <v>0.17877742221801018</v>
       </c>
       <c r="W41" s="13">
         <f>VLOOKUP($D41,Calcs!$A$21:$J$27,8,FALSE)</f>
@@ -16705,15 +16769,15 @@
       </c>
       <c r="Z41" s="13">
         <f t="shared" si="2"/>
-        <v>4.8801656663865704E-2</v>
+        <v>6.5942431286247036E-2</v>
       </c>
       <c r="AA41" s="13">
         <f t="shared" si="3"/>
-        <v>9.5158528986189015E-3</v>
+        <v>1.285813881727977E-2</v>
       </c>
       <c r="AB41" s="13">
         <f t="shared" si="4"/>
-        <v>1.4104525047360032E-3</v>
+        <v>1.9058506152094521E-3</v>
       </c>
     </row>
     <row r="42" spans="1:28" x14ac:dyDescent="0.25">
@@ -16724,7 +16788,7 @@
         <v>127</v>
       </c>
       <c r="C42" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="D42" t="s">
         <v>345</v>
@@ -16737,68 +16801,68 @@
         <v>1</v>
       </c>
       <c r="G42" s="7">
-        <f>SUMIFS('PNNL Office Measures'!$E$5:$E$69,'PNNL Office Measures'!$A$5:$A$69,$B42,'PNNL Office Measures'!$D$5:$D$69,"Hot &amp; Humid")</f>
-        <v>61907</v>
+        <f>SUMIFS('PNNL Office Measures'!$E$5:$E$69,'PNNL Office Measures'!$A$5:$A$69,$B42,'PNNL Office Measures'!$D$5:$D$69,"Hot &amp; Humid")-$F$32</f>
+        <v>0</v>
       </c>
       <c r="H42" s="7">
-        <f>SUMIFS('PNNL Office Measures'!$F$5:$F$69,'PNNL Office Measures'!$A$5:$A$69,$B42,'PNNL Office Measures'!$D$5:$D$69,"Hot &amp; Humid")</f>
-        <v>164980</v>
+        <f>SUMIFS('PNNL Office Measures'!$F$5:$F$69,'PNNL Office Measures'!$A$5:$A$69,$B42,'PNNL Office Measures'!$D$5:$D$69,"Hot &amp; Humid")-$G$32</f>
+        <v>36684</v>
       </c>
       <c r="I42">
         <f>SUMIFS('EPS Inputs'!$C$45:$C$99,'EPS Inputs'!$A$45:$A$99,"Hot &amp; Dry",'EPS Inputs'!$D$45:$D$99,$A42)</f>
         <v>1</v>
       </c>
       <c r="J42" s="7">
-        <f>SUMIFS('PNNL Office Measures'!$E$5:$E$69,'PNNL Office Measures'!$A$5:$A$69,$B42,'PNNL Office Measures'!$D$5:$D$69,"Hot &amp; Dry")</f>
-        <v>62463</v>
+        <f>SUMIFS('PNNL Office Measures'!$E$5:$E$69,'PNNL Office Measures'!$A$5:$A$69,$B42,'PNNL Office Measures'!$D$5:$D$69,"Hot &amp; Dry")-$F$33</f>
+        <v>0</v>
       </c>
       <c r="K42" s="7">
-        <f>SUMIFS('PNNL Office Measures'!$F$5:$F$69,'PNNL Office Measures'!$A$5:$A$69,$B42,'PNNL Office Measures'!$D$5:$D$69,"Hot &amp; Dry")</f>
-        <v>166463</v>
+        <f>SUMIFS('PNNL Office Measures'!$F$5:$F$69,'PNNL Office Measures'!$A$5:$A$69,$B42,'PNNL Office Measures'!$D$5:$D$69,"Hot &amp; Dry")-$G$33</f>
+        <v>37014</v>
       </c>
       <c r="L42">
         <f>SUMIFS('EPS Inputs'!$C$45:$C$99,'EPS Inputs'!$A$45:$A$99,"Marine",'EPS Inputs'!$D$45:$D$99,$A42)</f>
         <v>1</v>
       </c>
       <c r="M42" s="7">
-        <f>SUMIFS('PNNL Office Measures'!$E$5:$E$69,'PNNL Office Measures'!$A$5:$A$69,$B42,'PNNL Office Measures'!$D$5:$D$69,"Marine")</f>
-        <v>64690</v>
+        <f>SUMIFS('PNNL Office Measures'!$E$5:$E$69,'PNNL Office Measures'!$A$5:$A$69,$B42,'PNNL Office Measures'!$D$5:$D$69,"Marine")-$F$34</f>
+        <v>0</v>
       </c>
       <c r="N42" s="7">
-        <f>SUMIFS('PNNL Office Measures'!$F$5:$F$69,'PNNL Office Measures'!$A$5:$A$69,$B42,'PNNL Office Measures'!$D$5:$D$69,"Marine")</f>
-        <v>172397</v>
+        <f>SUMIFS('PNNL Office Measures'!$F$5:$F$69,'PNNL Office Measures'!$A$5:$A$69,$B42,'PNNL Office Measures'!$D$5:$D$69,"Marine")-$G$34</f>
+        <v>38333</v>
       </c>
       <c r="O42">
         <f>SUMIFS('EPS Inputs'!$C$45:$C$99,'EPS Inputs'!$A$45:$A$99,"Cold",'EPS Inputs'!$D$45:$D$99,$A42)</f>
         <v>1</v>
       </c>
       <c r="P42" s="7">
-        <f>SUMIFS('PNNL Office Measures'!$E$5:$E$69,'PNNL Office Measures'!$A$5:$A$69,$B42,'PNNL Office Measures'!$D$5:$D$69,"Cold")</f>
-        <v>61226</v>
+        <f>SUMIFS('PNNL Office Measures'!$E$5:$E$69,'PNNL Office Measures'!$A$5:$A$69,$B42,'PNNL Office Measures'!$D$5:$D$69,"Cold")-$F$35</f>
+        <v>0</v>
       </c>
       <c r="Q42" s="7">
-        <f>SUMIFS('PNNL Office Measures'!$F$5:$F$69,'PNNL Office Measures'!$A$5:$A$69,$B42,'PNNL Office Measures'!$D$5:$D$69,"Cold")</f>
-        <v>163167</v>
+        <f>SUMIFS('PNNL Office Measures'!$F$5:$F$69,'PNNL Office Measures'!$A$5:$A$69,$B42,'PNNL Office Measures'!$D$5:$D$69,"Cold")-$G$35</f>
+        <v>36281</v>
       </c>
       <c r="R42">
         <f>SUMIFS('EPS Inputs'!$C$45:$C$99,'EPS Inputs'!$A$45:$A$99,"Very Cold",'EPS Inputs'!$D$45:$D$99,$A42)</f>
         <v>1</v>
       </c>
       <c r="S42" s="7">
-        <f>SUMIFS('PNNL Office Measures'!$E$5:$E$69,'PNNL Office Measures'!$A$5:$A$69,$B42,'PNNL Office Measures'!$D$5:$D$69,"Very Cold")</f>
-        <v>60979</v>
+        <f>SUMIFS('PNNL Office Measures'!$E$5:$E$69,'PNNL Office Measures'!$A$5:$A$69,$B42,'PNNL Office Measures'!$D$5:$D$69,"Very Cold")-$F$36</f>
+        <v>0</v>
       </c>
       <c r="T42" s="7">
-        <f>SUMIFS('PNNL Office Measures'!$F$5:$F$69,'PNNL Office Measures'!$A$5:$A$69,$B42,'PNNL Office Measures'!$D$5:$D$69,"Very Cold")</f>
-        <v>162508</v>
+        <f>SUMIFS('PNNL Office Measures'!$F$5:$F$69,'PNNL Office Measures'!$A$5:$A$69,$B42,'PNNL Office Measures'!$D$5:$D$69,"Very Cold")-$G$36</f>
+        <v>36134</v>
       </c>
       <c r="U42" s="13">
         <f t="shared" si="0"/>
-        <v>5.5602383932595464E-2</v>
+        <v>0</v>
       </c>
       <c r="V42" s="13">
         <f t="shared" si="1"/>
-        <v>0.14817938280020687</v>
+        <v>4.452091732574489E-2</v>
       </c>
       <c r="W42" s="13">
         <f>VLOOKUP($D42,Calcs!$A$21:$J$27,8,FALSE)</f>
@@ -16814,15 +16878,15 @@
       </c>
       <c r="Z42" s="13">
         <f t="shared" si="2"/>
-        <v>4.5430789138880739E-2</v>
+        <v>0</v>
       </c>
       <c r="AA42" s="13">
         <f t="shared" si="3"/>
-        <v>8.8585662058858015E-3</v>
+        <v>0</v>
       </c>
       <c r="AB42" s="13">
         <f t="shared" si="4"/>
-        <v>1.3130285878289231E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:28" x14ac:dyDescent="0.25">
@@ -16833,7 +16897,7 @@
         <v>129</v>
       </c>
       <c r="C43" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="D43" t="s">
         <v>345</v>
@@ -16846,68 +16910,68 @@
         <v>1</v>
       </c>
       <c r="G43" s="7">
-        <f>SUMIFS('PNNL Office Measures'!$E$5:$E$69,'PNNL Office Measures'!$A$5:$A$69,$B43,'PNNL Office Measures'!$D$5:$D$69,"Hot &amp; Humid")</f>
-        <v>78581</v>
+        <f>SUMIFS('PNNL Office Measures'!$E$5:$E$69,'PNNL Office Measures'!$A$5:$A$69,$B43,'PNNL Office Measures'!$D$5:$D$69,"Hot &amp; Humid")-$F$32</f>
+        <v>16674</v>
       </c>
       <c r="H43" s="7">
-        <f>SUMIFS('PNNL Office Measures'!$F$5:$F$69,'PNNL Office Measures'!$A$5:$A$69,$B43,'PNNL Office Measures'!$D$5:$D$69,"Hot &amp; Humid")</f>
-        <v>154455</v>
+        <f>SUMIFS('PNNL Office Measures'!$F$5:$F$69,'PNNL Office Measures'!$A$5:$A$69,$B43,'PNNL Office Measures'!$D$5:$D$69,"Hot &amp; Humid")-$G$32</f>
+        <v>26159</v>
       </c>
       <c r="I43">
         <f>SUMIFS('EPS Inputs'!$C$45:$C$99,'EPS Inputs'!$A$45:$A$99,"Hot &amp; Dry",'EPS Inputs'!$D$45:$D$99,$A43)</f>
         <v>1</v>
       </c>
       <c r="J43" s="7">
-        <f>SUMIFS('PNNL Office Measures'!$E$5:$E$69,'PNNL Office Measures'!$A$5:$A$69,$B43,'PNNL Office Measures'!$D$5:$D$69,"Hot &amp; Dry")</f>
-        <v>79288</v>
+        <f>SUMIFS('PNNL Office Measures'!$E$5:$E$69,'PNNL Office Measures'!$A$5:$A$69,$B43,'PNNL Office Measures'!$D$5:$D$69,"Hot &amp; Dry")-$F$33</f>
+        <v>16825</v>
       </c>
       <c r="K43" s="7">
-        <f>SUMIFS('PNNL Office Measures'!$F$5:$F$69,'PNNL Office Measures'!$A$5:$A$69,$B43,'PNNL Office Measures'!$D$5:$D$69,"Hot &amp; Dry")</f>
-        <v>221372</v>
+        <f>SUMIFS('PNNL Office Measures'!$F$5:$F$69,'PNNL Office Measures'!$A$5:$A$69,$B43,'PNNL Office Measures'!$D$5:$D$69,"Hot &amp; Dry")-$G$33</f>
+        <v>91923</v>
       </c>
       <c r="L43">
         <f>SUMIFS('EPS Inputs'!$C$45:$C$99,'EPS Inputs'!$A$45:$A$99,"Marine",'EPS Inputs'!$D$45:$D$99,$A43)</f>
         <v>1</v>
       </c>
       <c r="M43" s="7">
-        <f>SUMIFS('PNNL Office Measures'!$E$5:$E$69,'PNNL Office Measures'!$A$5:$A$69,$B43,'PNNL Office Measures'!$D$5:$D$69,"Marine")</f>
-        <v>82114</v>
+        <f>SUMIFS('PNNL Office Measures'!$E$5:$E$69,'PNNL Office Measures'!$A$5:$A$69,$B43,'PNNL Office Measures'!$D$5:$D$69,"Marine")-$F$34</f>
+        <v>17424</v>
       </c>
       <c r="N43" s="7">
-        <f>SUMIFS('PNNL Office Measures'!$F$5:$F$69,'PNNL Office Measures'!$A$5:$A$69,$B43,'PNNL Office Measures'!$D$5:$D$69,"Marine")</f>
-        <v>203670</v>
+        <f>SUMIFS('PNNL Office Measures'!$F$5:$F$69,'PNNL Office Measures'!$A$5:$A$69,$B43,'PNNL Office Measures'!$D$5:$D$69,"Marine")-$G$34</f>
+        <v>69606</v>
       </c>
       <c r="O43">
         <f>SUMIFS('EPS Inputs'!$C$45:$C$99,'EPS Inputs'!$A$45:$A$99,"Cold",'EPS Inputs'!$D$45:$D$99,$A43)</f>
         <v>1</v>
       </c>
       <c r="P43" s="7">
-        <f>SUMIFS('PNNL Office Measures'!$E$5:$E$69,'PNNL Office Measures'!$A$5:$A$69,$B43,'PNNL Office Measures'!$D$5:$D$69,"Cold")</f>
-        <v>77717</v>
+        <f>SUMIFS('PNNL Office Measures'!$E$5:$E$69,'PNNL Office Measures'!$A$5:$A$69,$B43,'PNNL Office Measures'!$D$5:$D$69,"Cold")-$F$35</f>
+        <v>16491</v>
       </c>
       <c r="Q43" s="7">
-        <f>SUMIFS('PNNL Office Measures'!$F$5:$F$69,'PNNL Office Measures'!$A$5:$A$69,$B43,'PNNL Office Measures'!$D$5:$D$69,"Cold")</f>
-        <v>267669</v>
+        <f>SUMIFS('PNNL Office Measures'!$F$5:$F$69,'PNNL Office Measures'!$A$5:$A$69,$B43,'PNNL Office Measures'!$D$5:$D$69,"Cold")-$G$35</f>
+        <v>140783</v>
       </c>
       <c r="R43">
         <f>SUMIFS('EPS Inputs'!$C$45:$C$99,'EPS Inputs'!$A$45:$A$99,"Very Cold",'EPS Inputs'!$D$45:$D$99,$A43)</f>
         <v>1</v>
       </c>
       <c r="S43" s="7">
-        <f>SUMIFS('PNNL Office Measures'!$E$5:$E$69,'PNNL Office Measures'!$A$5:$A$69,$B43,'PNNL Office Measures'!$D$5:$D$69,"Very Cold")</f>
-        <v>77403</v>
+        <f>SUMIFS('PNNL Office Measures'!$E$5:$E$69,'PNNL Office Measures'!$A$5:$A$69,$B43,'PNNL Office Measures'!$D$5:$D$69,"Very Cold")-$F$36</f>
+        <v>16424</v>
       </c>
       <c r="T43" s="7">
-        <f>SUMIFS('PNNL Office Measures'!$F$5:$F$69,'PNNL Office Measures'!$A$5:$A$69,$B43,'PNNL Office Measures'!$D$5:$D$69,"Very Cold")</f>
-        <v>222928</v>
+        <f>SUMIFS('PNNL Office Measures'!$F$5:$F$69,'PNNL Office Measures'!$A$5:$A$69,$B43,'PNNL Office Measures'!$D$5:$D$69,"Very Cold")-$G$36</f>
+        <v>96554</v>
       </c>
       <c r="U43" s="13">
         <f t="shared" si="0"/>
-        <v>7.0578563365066072E-2</v>
+        <v>2.0236313318056302E-2</v>
       </c>
       <c r="V43" s="13">
         <f t="shared" si="1"/>
-        <v>0.19883837987652792</v>
+        <v>0.10728514843877061</v>
       </c>
       <c r="W43" s="13">
         <f>VLOOKUP($D43,Calcs!$A$21:$J$27,8,FALSE)</f>
@@ -16923,15 +16987,15 @@
       </c>
       <c r="Z43" s="13">
         <f t="shared" si="2"/>
-        <v>5.7667308542930243E-2</v>
+        <v>1.6534393280968545E-2</v>
       </c>
       <c r="AA43" s="13">
         <f t="shared" si="3"/>
-        <v>1.1244569604132063E-2</v>
+        <v>3.2240473989094739E-3</v>
       </c>
       <c r="AB43" s="13">
         <f t="shared" si="4"/>
-        <v>1.6666852180037643E-3</v>
+        <v>4.7787263817828171E-4</v>
       </c>
     </row>
     <row r="44" spans="1:28" x14ac:dyDescent="0.25">
@@ -16942,7 +17006,7 @@
         <v>131</v>
       </c>
       <c r="C44" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="D44" t="s">
         <v>347</v>
@@ -17012,11 +17076,11 @@
       </c>
       <c r="U44" s="13">
         <f t="shared" si="0"/>
-        <v>1.8761196783431675E-2</v>
+        <v>2.566999336520593E-2</v>
       </c>
       <c r="V44" s="13">
         <f t="shared" si="1"/>
-        <v>1.3614427035684652E-2</v>
+        <v>1.8719483695534223E-2</v>
       </c>
       <c r="W44" s="13">
         <f>VLOOKUP($D44,Calcs!$A$21:$J$27,8,FALSE)</f>
@@ -17032,15 +17096,15 @@
       </c>
       <c r="Z44" s="13">
         <f t="shared" si="2"/>
-        <v>9.5056730369387152E-3</v>
+        <v>1.3006129971704338E-2</v>
       </c>
       <c r="AA44" s="13">
         <f t="shared" si="3"/>
-        <v>9.1572508109606984E-3</v>
+        <v>1.2529401523493371E-2</v>
       </c>
       <c r="AB44" s="13">
         <f t="shared" si="4"/>
-        <v>9.8272935532261153E-5</v>
+        <v>1.3446187000822152E-4</v>
       </c>
     </row>
     <row r="45" spans="1:28" x14ac:dyDescent="0.25">
@@ -17051,7 +17115,7 @@
         <v>133</v>
       </c>
       <c r="C45" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="D45" t="s">
         <v>355</v>
@@ -17125,7 +17189,7 @@
       </c>
       <c r="V45" s="13">
         <f t="shared" si="1"/>
-        <v>6.8558670660983452E-4</v>
+        <v>1.0184824810839967E-3</v>
       </c>
       <c r="W45" s="13">
         <f>VLOOKUP($D45,Calcs!$A$21:$J$27,8,FALSE)</f>
@@ -17160,7 +17224,7 @@
         <v>135</v>
       </c>
       <c r="C46" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="D46" t="s">
         <v>347</v>
@@ -17230,11 +17294,11 @@
       </c>
       <c r="U46" s="13">
         <f t="shared" si="0"/>
-        <v>1.3213566748221078E-3</v>
+        <v>2.0005960684585547E-3</v>
       </c>
       <c r="V46" s="13">
         <f t="shared" si="1"/>
-        <v>8.9036671710362937E-4</v>
+        <v>1.3480570293132096E-3</v>
       </c>
       <c r="W46" s="13">
         <f>VLOOKUP($D46,Calcs!$A$21:$J$27,8,FALSE)</f>
@@ -17250,15 +17314,15 @@
       </c>
       <c r="Z46" s="13">
         <f t="shared" si="2"/>
-        <v>6.6948738190986796E-4</v>
+        <v>1.0136353413523346E-3</v>
       </c>
       <c r="AA46" s="13">
         <f t="shared" si="3"/>
-        <v>6.4494790080602883E-4</v>
+        <v>9.7648141436667548E-4</v>
       </c>
       <c r="AB46" s="13">
         <f t="shared" si="4"/>
-        <v>6.9213921062110402E-6</v>
+        <v>1.0479312739544809E-5</v>
       </c>
     </row>
     <row r="47" spans="1:28" x14ac:dyDescent="0.25">
@@ -17269,7 +17333,7 @@
         <v>137</v>
       </c>
       <c r="C47" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="D47" t="s">
         <v>349</v>
@@ -17339,11 +17403,11 @@
       </c>
       <c r="U47" s="13">
         <f t="shared" si="0"/>
-        <v>6.1140814711311137E-3</v>
+        <v>9.0836570373325973E-3</v>
       </c>
       <c r="V47" s="13">
         <f t="shared" si="1"/>
-        <v>3.3719072518623569E-3</v>
+        <v>5.014240597305721E-3</v>
       </c>
       <c r="W47" s="13">
         <f>VLOOKUP($D47,Calcs!$A$21:$J$27,8,FALSE)</f>
@@ -17359,15 +17423,15 @@
       </c>
       <c r="Z47" s="13">
         <f t="shared" si="2"/>
-        <v>5.0120167352119783E-3</v>
+        <v>7.446325552416035E-3</v>
       </c>
       <c r="AA47" s="13">
         <f t="shared" si="3"/>
-        <v>9.5526061537456021E-4</v>
+        <v>1.4192254146931551E-3</v>
       </c>
       <c r="AB47" s="13">
         <f t="shared" si="4"/>
-        <v>1.4680412054457527E-4</v>
+        <v>2.1810607022340695E-4</v>
       </c>
     </row>
     <row r="48" spans="1:28" x14ac:dyDescent="0.25">
@@ -17378,7 +17442,7 @@
         <v>139</v>
       </c>
       <c r="C48" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="D48" t="s">
         <v>347</v>
@@ -17448,11 +17512,11 @@
       </c>
       <c r="U48" s="13">
         <f t="shared" si="0"/>
-        <v>1.4465896222926246E-2</v>
+        <v>2.1500409601266687E-2</v>
       </c>
       <c r="V48" s="13">
         <f t="shared" si="1"/>
-        <v>1.0636026096332674E-2</v>
+        <v>1.5817826228485501E-2</v>
       </c>
       <c r="W48" s="13">
         <f>VLOOKUP($D48,Calcs!$A$21:$J$27,8,FALSE)</f>
@@ -17468,15 +17532,15 @@
       </c>
       <c r="Z48" s="13">
         <f t="shared" si="2"/>
-        <v>7.3293874196159649E-3</v>
+        <v>1.0893540864641789E-2</v>
       </c>
       <c r="AA48" s="13">
         <f t="shared" si="3"/>
-        <v>7.0607350611901912E-3</v>
+        <v>1.0494247543475407E-2</v>
       </c>
       <c r="AB48" s="13">
         <f t="shared" si="4"/>
-        <v>7.5773742120089862E-5</v>
+        <v>1.1262119314949217E-4</v>
       </c>
     </row>
     <row r="49" spans="1:28" x14ac:dyDescent="0.25">
@@ -17487,7 +17551,7 @@
         <v>141</v>
       </c>
       <c r="C49" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="D49" t="s">
         <v>347</v>
@@ -17557,11 +17621,11 @@
       </c>
       <c r="U49" s="13">
         <f t="shared" si="0"/>
-        <v>1.4228522215796853E-2</v>
+        <v>2.113735735716404E-2</v>
       </c>
       <c r="V49" s="13">
         <f t="shared" si="1"/>
-        <v>4.648404636395851E-3</v>
+        <v>6.9124751868122093E-3</v>
       </c>
       <c r="W49" s="13">
         <f>VLOOKUP($D49,Calcs!$A$21:$J$27,8,FALSE)</f>
@@ -17577,15 +17641,15 @@
       </c>
       <c r="Z49" s="13">
         <f t="shared" si="2"/>
-        <v>7.2091179226704064E-3</v>
+        <v>1.0709594394296447E-2</v>
       </c>
       <c r="AA49" s="13">
         <f t="shared" si="3"/>
-        <v>6.9448739386627498E-3</v>
+        <v>1.0317043471949115E-2</v>
       </c>
       <c r="AB49" s="13">
         <f t="shared" si="4"/>
-        <v>7.4530354463697794E-5</v>
+        <v>1.1071949091847831E-4</v>
       </c>
     </row>
     <row r="50" spans="1:28" x14ac:dyDescent="0.25">
@@ -17593,84 +17657,84 @@
         <v>143</v>
       </c>
       <c r="B50" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C50" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="D50" t="s">
         <v>351</v>
       </c>
       <c r="E50" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="F50">
         <f>SUMIFS('EPS Inputs'!$C$45:$C$99,'EPS Inputs'!$A$45:$A$99,"Hot &amp; Humid",'EPS Inputs'!$D$45:$D$99,$A50)</f>
         <v>0</v>
       </c>
       <c r="G50" s="7">
-        <f>SUMIFS('PNNL Office Measures'!$E$5:$E$69,'PNNL Office Measures'!$A$5:$A$69,$B50,'PNNL Office Measures'!$D$5:$D$69,"Hot &amp; Humid")</f>
-        <v>4019</v>
+        <f>SUMIFS('PNNL Office Measures'!$E$5:$E$69,'PNNL Office Measures'!$A$5:$A$69,$B50,'PNNL Office Measures'!$D$5:$D$69,"Hot &amp; Humid")-$F$32</f>
+        <v>139688</v>
       </c>
       <c r="H50" s="7">
-        <f>SUMIFS('PNNL Office Measures'!$F$5:$F$69,'PNNL Office Measures'!$A$5:$A$69,$B50,'PNNL Office Measures'!$D$5:$D$69,"Hot &amp; Humid")</f>
-        <v>29420</v>
+        <f>SUMIFS('PNNL Office Measures'!$F$5:$F$69,'PNNL Office Measures'!$A$5:$A$69,$B50,'PNNL Office Measures'!$D$5:$D$69,"Hot &amp; Humid")-$G$32</f>
+        <v>73864</v>
       </c>
       <c r="I50">
         <f>SUMIFS('EPS Inputs'!$C$45:$C$99,'EPS Inputs'!$A$45:$A$99,"Hot &amp; Dry",'EPS Inputs'!$D$45:$D$99,$A50)</f>
         <v>0</v>
       </c>
       <c r="J50" s="7">
-        <f>SUMIFS('PNNL Office Measures'!$E$5:$E$69,'PNNL Office Measures'!$A$5:$A$69,$B50,'PNNL Office Measures'!$D$5:$D$69,"Hot &amp; Dry")</f>
-        <v>4635</v>
+        <f>SUMIFS('PNNL Office Measures'!$E$5:$E$69,'PNNL Office Measures'!$A$5:$A$69,$B50,'PNNL Office Measures'!$D$5:$D$69,"Hot &amp; Dry")-$F$33</f>
+        <v>161384</v>
       </c>
       <c r="K50" s="7">
-        <f>SUMIFS('PNNL Office Measures'!$F$5:$F$69,'PNNL Office Measures'!$A$5:$A$69,$B50,'PNNL Office Measures'!$D$5:$D$69,"Hot &amp; Dry")</f>
-        <v>42167</v>
+        <f>SUMIFS('PNNL Office Measures'!$F$5:$F$69,'PNNL Office Measures'!$A$5:$A$69,$B50,'PNNL Office Measures'!$D$5:$D$69,"Hot &amp; Dry")-$G$33</f>
+        <v>74529</v>
       </c>
       <c r="L50">
         <f>SUMIFS('EPS Inputs'!$C$45:$C$99,'EPS Inputs'!$A$45:$A$99,"Marine",'EPS Inputs'!$D$45:$D$99,$A50)</f>
         <v>1</v>
       </c>
       <c r="M50" s="7">
-        <f>SUMIFS('PNNL Office Measures'!$E$5:$E$69,'PNNL Office Measures'!$A$5:$A$69,$B50,'PNNL Office Measures'!$D$5:$D$69,"Marine")</f>
-        <v>5400</v>
+        <f>SUMIFS('PNNL Office Measures'!$E$5:$E$69,'PNNL Office Measures'!$A$5:$A$69,$B50,'PNNL Office Measures'!$D$5:$D$69,"Marine")-$F$34</f>
+        <v>165600</v>
       </c>
       <c r="N50" s="7">
-        <f>SUMIFS('PNNL Office Measures'!$F$5:$F$69,'PNNL Office Measures'!$A$5:$A$69,$B50,'PNNL Office Measures'!$D$5:$D$69,"Marine")</f>
-        <v>38795</v>
+        <f>SUMIFS('PNNL Office Measures'!$F$5:$F$69,'PNNL Office Measures'!$A$5:$A$69,$B50,'PNNL Office Measures'!$D$5:$D$69,"Marine")-$G$34</f>
+        <v>77184</v>
       </c>
       <c r="O50">
         <f>SUMIFS('EPS Inputs'!$C$45:$C$99,'EPS Inputs'!$A$45:$A$99,"Cold",'EPS Inputs'!$D$45:$D$99,$A50)</f>
         <v>1</v>
       </c>
       <c r="P50" s="7">
-        <f>SUMIFS('PNNL Office Measures'!$E$5:$E$69,'PNNL Office Measures'!$A$5:$A$69,$B50,'PNNL Office Measures'!$D$5:$D$69,"Cold")</f>
-        <v>6247</v>
+        <f>SUMIFS('PNNL Office Measures'!$E$5:$E$69,'PNNL Office Measures'!$A$5:$A$69,$B50,'PNNL Office Measures'!$D$5:$D$69,"Cold")-$F$35</f>
+        <v>173248</v>
       </c>
       <c r="Q50" s="7">
-        <f>SUMIFS('PNNL Office Measures'!$F$5:$F$69,'PNNL Office Measures'!$A$5:$A$69,$B50,'PNNL Office Measures'!$D$5:$D$69,"Cold")</f>
-        <v>50985</v>
+        <f>SUMIFS('PNNL Office Measures'!$F$5:$F$69,'PNNL Office Measures'!$A$5:$A$69,$B50,'PNNL Office Measures'!$D$5:$D$69,"Cold")-$G$35</f>
+        <v>73052</v>
       </c>
       <c r="R50">
         <f>SUMIFS('EPS Inputs'!$C$45:$C$99,'EPS Inputs'!$A$45:$A$99,"Very Cold",'EPS Inputs'!$D$45:$D$99,$A50)</f>
         <v>1</v>
       </c>
       <c r="S50" s="7">
-        <f>SUMIFS('PNNL Office Measures'!$E$5:$E$69,'PNNL Office Measures'!$A$5:$A$69,$B50,'PNNL Office Measures'!$D$5:$D$69,"Very Cold")</f>
-        <v>5656</v>
+        <f>SUMIFS('PNNL Office Measures'!$E$5:$E$69,'PNNL Office Measures'!$A$5:$A$69,$B50,'PNNL Office Measures'!$D$5:$D$69,"Very Cold")-$F$36</f>
+        <v>180602</v>
       </c>
       <c r="T50" s="7">
-        <f>SUMIFS('PNNL Office Measures'!$F$5:$F$69,'PNNL Office Measures'!$A$5:$A$69,$B50,'PNNL Office Measures'!$D$5:$D$69,"Very Cold")</f>
-        <v>42463</v>
+        <f>SUMIFS('PNNL Office Measures'!$F$5:$F$69,'PNNL Office Measures'!$A$5:$A$69,$B50,'PNNL Office Measures'!$D$5:$D$69,"Very Cold")-$G$36</f>
+        <v>72757</v>
       </c>
       <c r="U50" s="13">
         <f t="shared" si="0"/>
-        <v>3.2584128844980417E-3</v>
+        <v>0.1151417694856241</v>
       </c>
       <c r="V50" s="13">
         <f t="shared" si="1"/>
-        <v>2.6283874726998013E-2</v>
+        <v>4.8692711496011676E-2</v>
       </c>
       <c r="W50" s="13">
         <f>VLOOKUP($D50,Calcs!$A$21:$J$27,8,FALSE)</f>
@@ -17686,65 +17750,65 @@
       </c>
       <c r="Z50" s="13">
         <f t="shared" si="2"/>
-        <v>1.7730010125589174E-3</v>
+        <v>6.2652119642991694E-2</v>
       </c>
       <c r="AA50" s="13">
         <f t="shared" si="3"/>
-        <v>1.4316634160465903E-3</v>
+        <v>5.0590353302274002E-2</v>
       </c>
       <c r="AB50" s="13">
         <f t="shared" si="4"/>
-        <v>5.3748455892534113E-5</v>
+        <v>1.8992965403584097E-3</v>
       </c>
     </row>
     <row r="51" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="G51" s="7">
         <f>SUMPRODUCT(F40:F50,G40:G50)+SUMPRODUCT(F40:F50,H40:H50)</f>
-        <v>857499</v>
+        <v>477093</v>
       </c>
       <c r="J51" s="7">
         <f>SUMPRODUCT(I40:I50,J40:J50)+SUMPRODUCT(I40:I50,K40:K50)</f>
-        <v>1383954</v>
+        <v>1000130</v>
       </c>
       <c r="M51" s="7">
         <f>SUMPRODUCT(L40:L50,M40:M50)+SUMPRODUCT(L40:L50,N40:N50)</f>
-        <v>1217854</v>
+        <v>1018935</v>
       </c>
       <c r="P51" s="7">
         <f>SUMPRODUCT(O40:O50,P40:P50)+SUMPRODUCT(O40:O50,Q40:Q50)</f>
-        <v>1238255</v>
+        <v>1051099</v>
       </c>
       <c r="S51" s="7">
         <f>SUMPRODUCT(R40:R50,S40:S50)+SUMPRODUCT(R40:R50,T40:T50)</f>
-        <v>1225958</v>
+        <v>1056492</v>
       </c>
       <c r="U51" s="13">
         <f>SUM(U40:U50)</f>
-        <v>0.32400416417191263</v>
+        <v>0.39755245056510913</v>
       </c>
       <c r="V51" s="13">
         <f>SUM(V40:V50)</f>
-        <v>0.6759958358280872</v>
+        <v>0.60244754943489109</v>
       </c>
       <c r="Z51" s="13">
         <f>SUM(Z40:Z50)</f>
-        <v>0.26334422640900695</v>
+        <v>0.29027410394788289</v>
       </c>
       <c r="AA51" s="13">
         <f>SUM(AA40:AA50)</f>
-        <v>5.5813720451677588E-2</v>
+        <v>0.10240893888644097</v>
       </c>
       <c r="AB51" s="13">
         <f>SUM(AB40:AB50)</f>
-        <v>4.8462173112280597E-3</v>
+        <v>4.8694077307852874E-3</v>
       </c>
     </row>
     <row r="54" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A54" s="9" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="B54" s="10"/>
       <c r="C54" s="10"/>
@@ -17759,27 +17823,27 @@
     <row r="55" spans="1:28" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="6"/>
       <c r="B55" s="6" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="F55" s="6" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="G55" s="6" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="56" spans="1:28" ht="45" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="B56" s="13">
         <f>INDEX('EPS Inputs'!$B$5:$BA$5,MATCH("ISIC 28",'EPS Inputs'!$B$4:$BA$4,0))</f>
@@ -17798,15 +17862,15 @@
         <v>0.73624568700000004</v>
       </c>
       <c r="F56" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="G56" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="57" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="58" spans="1:28" x14ac:dyDescent="0.25">
@@ -18411,11 +18475,11 @@
       </c>
       <c r="F78" s="16">
         <f t="shared" ref="F78:G97" si="6">SUMIFS($Z$40:$Z$50,$E$40:$E$50,$A78)+IF($A78="ISIC 41T43",$V$51,0)+IF($A78="ISIC 45T47",$AA$51,0)+IF($A78="ISIC 49",$AB$51,0)</f>
-        <v>0</v>
+        <v>6.2652119642991694E-2</v>
       </c>
       <c r="G78" s="16">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>6.2652119642991694E-2</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
@@ -18440,11 +18504,11 @@
       </c>
       <c r="F79" s="16">
         <f t="shared" si="6"/>
-        <v>0.15189975434567671</v>
+        <v>8.2476824567215584E-2</v>
       </c>
       <c r="G79" s="16">
         <f t="shared" si="6"/>
-        <v>0.15189975434567671</v>
+        <v>8.2476824567215584E-2</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -18469,11 +18533,11 @@
       </c>
       <c r="F80" s="16">
         <f t="shared" si="6"/>
-        <v>2.4713665761134956E-2</v>
+        <v>3.5622900571994909E-2</v>
       </c>
       <c r="G80" s="16">
         <f t="shared" si="6"/>
-        <v>2.4713665761134956E-2</v>
+        <v>3.5622900571994909E-2</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -18498,11 +18562,11 @@
       </c>
       <c r="F81" s="16">
         <f t="shared" si="6"/>
-        <v>6.7850177477708955E-3</v>
+        <v>7.446325552416035E-3</v>
       </c>
       <c r="G81" s="16">
         <f t="shared" si="6"/>
-        <v>6.7850177477708955E-3</v>
+        <v>7.446325552416035E-3</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
@@ -18730,11 +18794,11 @@
       </c>
       <c r="F89" s="16">
         <f t="shared" si="6"/>
-        <v>0.75594162438251167</v>
+        <v>0.70452348304815571</v>
       </c>
       <c r="G89" s="16">
         <f t="shared" si="6"/>
-        <v>0.75594162438251167</v>
+        <v>0.70452348304815571</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
@@ -18759,11 +18823,11 @@
       </c>
       <c r="F90" s="16">
         <f t="shared" si="6"/>
-        <v>5.5813720451677588E-2</v>
+        <v>0.10240893888644097</v>
       </c>
       <c r="G90" s="16">
         <f t="shared" si="6"/>
-        <v>5.5813720451677588E-2</v>
+        <v>0.10240893888644097</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -18788,11 +18852,11 @@
       </c>
       <c r="F91" s="16">
         <f t="shared" si="6"/>
-        <v>4.8462173112280597E-3</v>
+        <v>4.8694077307852874E-3</v>
       </c>
       <c r="G91" s="16">
         <f t="shared" si="6"/>
-        <v>4.8462173112280597E-3</v>
+        <v>4.8694077307852874E-3</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
@@ -19339,11 +19403,11 @@
       </c>
       <c r="F110" s="13">
         <f t="shared" si="8"/>
-        <v>0.99999999999999978</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="G110" s="13">
         <f t="shared" si="8"/>
-        <v>0.99999999999999978</v>
+        <v>1.0000000000000002</v>
       </c>
     </row>
   </sheetData>
@@ -19368,18 +19432,18 @@
   <sheetData>
     <row r="1" spans="1:3" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="B2">
         <f>SUM('SoBRCbIC-urbanresidential'!B2:BA2)</f>
@@ -19392,7 +19456,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="B3">
         <f>SUM('SoBRCbIC-urbanresidential'!B3:BA3)</f>
@@ -19405,7 +19469,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="B4">
         <f>SUM('SoBRCbIC-urbanresidential'!B4:BA4)</f>
@@ -19418,7 +19482,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="B5">
         <f>SUM('SoBRCbIC-urbanresidential'!B5:BA5)</f>
@@ -19431,7 +19495,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="B6">
         <f>SUM('SoBRCbIC-urbanresidential'!B6:BA6)</f>
@@ -19444,7 +19508,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="B7">
         <f>SUM('SoBRCbIC-urbanresidential'!B7:BA7)</f>
@@ -19457,7 +19521,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="B8">
         <f>SUM('SoBRCbIC-ruralresidential'!B2:BA2)</f>
@@ -19470,7 +19534,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="B9">
         <f>SUM('SoBRCbIC-ruralresidential'!B3:BA3)</f>
@@ -19483,7 +19547,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="B10">
         <f>SUM('SoBRCbIC-ruralresidential'!B4:BA4)</f>
@@ -19496,7 +19560,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="B11">
         <f>SUM('SoBRCbIC-ruralresidential'!B5:BA5)</f>
@@ -19509,7 +19573,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="B12">
         <f>SUM('SoBRCbIC-ruralresidential'!B6:BA6)</f>
@@ -19522,7 +19586,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="B13">
         <f>SUM('SoBRCbIC-ruralresidential'!B7:BA7)</f>
@@ -19535,11 +19599,11 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="B14">
         <f>SUM('SoBRCbIC-commercial'!B2:BA2)</f>
-        <v>0.99999999999999978</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="C14">
         <f t="shared" si="0"/>
@@ -19548,11 +19612,11 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="B15">
         <f>SUM('SoBRCbIC-commercial'!B3:BA3)</f>
-        <v>0.99999999999999978</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="C15">
         <f t="shared" si="0"/>
@@ -19561,7 +19625,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="B16">
         <f>SUM('SoBRCbIC-commercial'!B4:BA4)</f>
@@ -19574,7 +19638,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="B17">
         <f>SUM('SoBRCbIC-commercial'!B5:BA5)</f>
@@ -19587,7 +19651,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="B18">
         <f>SUM('SoBRCbIC-commercial'!B6:BA6)</f>
@@ -19600,7 +19664,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="B19">
         <f>SUM('SoBRCbIC-commercial'!B7:BA7)</f>
@@ -19613,7 +19677,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="B20">
         <f>INDEX('EPS Inputs'!$B$5:$BA$5,MATCH("ISIC 28",'EPS Inputs'!$B$4:$BA$4,0))+INDEX('EPS Inputs'!$B$5:$BA$5,MATCH("ISIC 41T43",'EPS Inputs'!$B$4:$BA$4,0))</f>
@@ -19626,7 +19690,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="B21">
         <f>INDEX('EPS Inputs'!$B$6:$BA$6,MATCH("ISIC 28",'EPS Inputs'!$B$4:$BA$4,0))+INDEX('EPS Inputs'!$B$6:$BA$6,MATCH("ISIC 41T43",'EPS Inputs'!$B$4:$BA$4,0))</f>
@@ -19639,7 +19703,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="B22">
         <f>INDEX('EPS Inputs'!$B$14:$BA$14,MATCH("ISIC 28",'EPS Inputs'!$B$13:$BA$13,0))+INDEX('EPS Inputs'!$B$14:$BA$14,MATCH("ISIC 41T43",'EPS Inputs'!$B$13:$BA$13,0))</f>
@@ -19652,7 +19716,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="B23">
         <f>INDEX('EPS Inputs'!$B$15:$BA$15,MATCH("ISIC 28",'EPS Inputs'!$B$13:$BA$13,0))+INDEX('EPS Inputs'!$B$15:$BA$15,MATCH("ISIC 41T43",'EPS Inputs'!$B$13:$BA$13,0))</f>
@@ -19665,11 +19729,11 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="B24">
         <f>Calcs!U51+Calcs!V51</f>
-        <v>0.99999999999999978</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="C24">
         <f t="shared" si="1"/>
@@ -19678,7 +19742,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="B25">
         <f>SUM(Calcs!D32:D36)</f>
@@ -19691,7 +19755,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="B26">
         <f>Calcs!B16</f>
@@ -19704,7 +19768,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="B27">
         <f>Calcs!H21+Calcs!I21+Calcs!J21</f>
@@ -19717,7 +19781,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="B28">
         <f>Calcs!H22+Calcs!I22+Calcs!J22</f>
@@ -19730,7 +19794,7 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="B29">
         <f>Calcs!H23+Calcs!I23+Calcs!J23</f>
@@ -19743,7 +19807,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="B30">
         <f>Calcs!H24+Calcs!I24+Calcs!J24</f>
@@ -19756,7 +19820,7 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="B31">
         <f>Calcs!H25+Calcs!I25+Calcs!J25</f>
@@ -19769,7 +19833,7 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="C33" s="1">
         <f>SUM(C2:C31)</f>

--- a/InputData/bldgs/SoBRCbIC/Shr of Bldg Retrofitting Costs by ISIC Code.xlsx
+++ b/InputData/bldgs/SoBRCbIC/Shr of Bldg Retrofitting Costs by ISIC Code.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\.claude\worktrees\retrofit-isic-split\InputData\bldgs\SoBRCbIC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11FF655D-55BE-4444-9815-051229B28EE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F66F1FE-8147-4A4B-827E-0BE34B06749E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -139,7 +139,7 @@
     <t>Table 6 (p. 31), typed on the "BEEx 2015 MF Costs" tab: citywide cost of the measures recommended in NYC energy audits, by category. These are audit recommendations for large NYC buildings, not deep retrofits. Domestic hot water, lighting and "other" are left out, as BRESaC does for its multifamily cost.</t>
   </si>
   <si>
-    <t>The published SoBCaICbIC values are copied to the "EPS Inputs" tab; the heating and cooling rows give the equipment part of an installed heating or cooling system. Update the tab if SoBCaICbIC changes.</t>
+    <t>The published SoBCaICbIC values are copied to the "EPS Inputs" tab; the heating and cooling rows give the equipment part of an installed heating or cooling system (everything not sent to installation). Update the tab if SoBCaICbIC changes.</t>
   </si>
   <si>
     <t>Commercial retrofit: equipment and installation cost of each measure</t>
@@ -1322,7 +1322,7 @@
 cooling</t>
   </si>
   <si>
-    <t>Share of the equipment part that is bought from the HVAC maker (SoBCaICbIC, ISIC 28 column)</t>
+    <t>Equipment part of an installed system: everything SoBCaICbIC does not send to installation (1 - its ISIC 41T43 share)</t>
   </si>
   <si>
     <t>n/a</t>
@@ -1395,16 +1395,16 @@
     <t>commercial Other: row sums to 100% (or 0% for rows SoBCaICbIC leaves empty)</t>
   </si>
   <si>
-    <t>SoBCaICbIC urbanresidential Heating: only ISIC 28 and 41T43 are nonzero (the residential formula assumes it)</t>
-  </si>
-  <si>
-    <t>SoBCaICbIC urbanresidential Cooling: only ISIC 28 and 41T43 are nonzero (the residential formula assumes it)</t>
-  </si>
-  <si>
-    <t>SoBCaICbIC ruralresidential Heating: only ISIC 28 and 41T43 are nonzero (the residential formula assumes it)</t>
-  </si>
-  <si>
-    <t>SoBCaICbIC ruralresidential Cooling: only ISIC 28 and 41T43 are nonzero (the residential formula assumes it)</t>
+    <t>SoBCaICbIC urbanresidential Heating: only the HVAC maker, trade, freight and installation are nonzero (the residential formula assumes it)</t>
+  </si>
+  <si>
+    <t>SoBCaICbIC urbanresidential Cooling: only the HVAC maker, trade, freight and installation are nonzero (the residential formula assumes it)</t>
+  </si>
+  <si>
+    <t>SoBCaICbIC ruralresidential Heating: only the HVAC maker, trade, freight and installation are nonzero (the residential formula assumes it)</t>
+  </si>
+  <si>
+    <t>SoBCaICbIC ruralresidential Cooling: only the HVAC maker, trade, freight and installation are nonzero (the residential formula assumes it)</t>
   </si>
   <si>
     <t>Commercial equipment + installation shares add to 100%</t>
@@ -3043,7 +3043,7 @@
       </c>
       <c r="X5">
         <f>'EPS Inputs'!X8</f>
-        <v>1</v>
+        <v>0.399985111</v>
       </c>
       <c r="Y5">
         <f>'EPS Inputs'!Y8</f>
@@ -3083,11 +3083,11 @@
       </c>
       <c r="AH5">
         <f>'EPS Inputs'!AH8</f>
-        <v>0</v>
+        <v>0.55505099400000002</v>
       </c>
       <c r="AI5">
         <f>'EPS Inputs'!AI8</f>
-        <v>0</v>
+        <v>4.4963894999999997E-2</v>
       </c>
       <c r="AJ5">
         <f>'EPS Inputs'!AJ8</f>
@@ -3256,7 +3256,7 @@
       </c>
       <c r="X6">
         <f>'EPS Inputs'!X9</f>
-        <v>0.75435141900000002</v>
+        <v>0.41594354500000003</v>
       </c>
       <c r="Y6">
         <f>'EPS Inputs'!Y9</f>
@@ -3296,11 +3296,11 @@
       </c>
       <c r="AH6">
         <f>'EPS Inputs'!AH9</f>
-        <v>0</v>
+        <v>0.33246167500000001</v>
       </c>
       <c r="AI6">
         <f>'EPS Inputs'!AI9</f>
-        <v>0</v>
+        <v>5.9461990000000001E-3</v>
       </c>
       <c r="AJ6">
         <f>'EPS Inputs'!AJ9</f>
@@ -3469,7 +3469,7 @@
       </c>
       <c r="X7">
         <f>'EPS Inputs'!X10</f>
-        <v>0.75435141900000002</v>
+        <v>0.39439856499999998</v>
       </c>
       <c r="Y7">
         <f>'EPS Inputs'!Y10</f>
@@ -3509,11 +3509,11 @@
       </c>
       <c r="AH7">
         <f>'EPS Inputs'!AH10</f>
-        <v>0</v>
+        <v>0.34557880800000002</v>
       </c>
       <c r="AI7">
         <f>'EPS Inputs'!AI10</f>
-        <v>0</v>
+        <v>1.4374046E-2</v>
       </c>
       <c r="AJ7">
         <f>'EPS Inputs'!AJ10</f>
@@ -4495,7 +4495,7 @@
       </c>
       <c r="X5">
         <f>'EPS Inputs'!X17</f>
-        <v>1</v>
+        <v>0.399985111</v>
       </c>
       <c r="Y5">
         <f>'EPS Inputs'!Y17</f>
@@ -4535,11 +4535,11 @@
       </c>
       <c r="AH5">
         <f>'EPS Inputs'!AH17</f>
-        <v>0</v>
+        <v>0.55505099400000002</v>
       </c>
       <c r="AI5">
         <f>'EPS Inputs'!AI17</f>
-        <v>0</v>
+        <v>4.4963894999999997E-2</v>
       </c>
       <c r="AJ5">
         <f>'EPS Inputs'!AJ17</f>
@@ -4708,7 +4708,7 @@
       </c>
       <c r="X6">
         <f>'EPS Inputs'!X18</f>
-        <v>0.75435141900000002</v>
+        <v>0.41594354500000003</v>
       </c>
       <c r="Y6">
         <f>'EPS Inputs'!Y18</f>
@@ -4748,11 +4748,11 @@
       </c>
       <c r="AH6">
         <f>'EPS Inputs'!AH18</f>
-        <v>0</v>
+        <v>0.33246167500000001</v>
       </c>
       <c r="AI6">
         <f>'EPS Inputs'!AI18</f>
-        <v>0</v>
+        <v>5.9461990000000001E-3</v>
       </c>
       <c r="AJ6">
         <f>'EPS Inputs'!AJ18</f>
@@ -4921,7 +4921,7 @@
       </c>
       <c r="X7">
         <f>'EPS Inputs'!X19</f>
-        <v>0.75435141900000002</v>
+        <v>0.39439856499999998</v>
       </c>
       <c r="Y7">
         <f>'EPS Inputs'!Y19</f>
@@ -4961,11 +4961,11 @@
       </c>
       <c r="AH7">
         <f>'EPS Inputs'!AH19</f>
-        <v>0</v>
+        <v>0.34557880800000002</v>
       </c>
       <c r="AI7">
         <f>'EPS Inputs'!AI19</f>
-        <v>0</v>
+        <v>1.4374046E-2</v>
       </c>
       <c r="AJ7">
         <f>'EPS Inputs'!AJ19</f>
@@ -5947,7 +5947,7 @@
       </c>
       <c r="X5">
         <f>'EPS Inputs'!X26</f>
-        <v>0.407668947</v>
+        <v>0.28238603800000001</v>
       </c>
       <c r="Y5">
         <f>'EPS Inputs'!Y26</f>
@@ -5987,11 +5987,11 @@
       </c>
       <c r="AH5">
         <f>'EPS Inputs'!AH26</f>
-        <v>0</v>
+        <v>9.1251813000000001E-2</v>
       </c>
       <c r="AI5">
         <f>'EPS Inputs'!AI26</f>
-        <v>0</v>
+        <v>3.4031095999999997E-2</v>
       </c>
       <c r="AJ5">
         <f>'EPS Inputs'!AJ26</f>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="X6">
         <f>'EPS Inputs'!X27</f>
-        <v>0.75439887000000005</v>
+        <v>0.51313159200000003</v>
       </c>
       <c r="Y6">
         <f>'EPS Inputs'!Y27</f>
@@ -6196,15 +6196,15 @@
       </c>
       <c r="AG6">
         <f>'EPS Inputs'!AG27</f>
-        <v>0.24560113</v>
+        <v>0.245601131</v>
       </c>
       <c r="AH6">
         <f>'EPS Inputs'!AH27</f>
-        <v>0</v>
+        <v>0.227081377</v>
       </c>
       <c r="AI6">
         <f>'EPS Inputs'!AI27</f>
-        <v>0</v>
+        <v>1.41859E-2</v>
       </c>
       <c r="AJ6">
         <f>'EPS Inputs'!AJ27</f>
@@ -6373,7 +6373,7 @@
       </c>
       <c r="X7">
         <f>'EPS Inputs'!X28</f>
-        <v>0.75439887000000005</v>
+        <v>0.51142569199999999</v>
       </c>
       <c r="Y7">
         <f>'EPS Inputs'!Y28</f>
@@ -6409,15 +6409,15 @@
       </c>
       <c r="AG7">
         <f>'EPS Inputs'!AG28</f>
-        <v>0.24560113</v>
+        <v>0.245601131</v>
       </c>
       <c r="AH7">
         <f>'EPS Inputs'!AH28</f>
-        <v>0</v>
+        <v>0.23490525200000001</v>
       </c>
       <c r="AI7">
         <f>'EPS Inputs'!AI28</f>
-        <v>0</v>
+        <v>8.0679259999999996E-3</v>
       </c>
       <c r="AJ7">
         <f>'EPS Inputs'!AJ28</f>
@@ -11602,7 +11602,7 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>0.55028127100000002</v>
+        <v>0.25957514999999998</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -11629,10 +11629,10 @@
         <v>0.44971872899999998</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>0.28309632800000001</v>
       </c>
       <c r="AI5">
-        <v>0</v>
+        <v>7.6097930000000001E-3</v>
       </c>
       <c r="AJ5">
         <v>0</v>
@@ -11763,7 +11763,7 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>0.73624568700000004</v>
+        <v>0.347194577</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -11790,10 +11790,10 @@
         <v>0.26375431300000002</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>0.37896261199999998</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>1.0088498E-2</v>
       </c>
       <c r="AJ6">
         <v>0</v>
@@ -12082,7 +12082,7 @@
         <v>0</v>
       </c>
       <c r="X8">
-        <v>1</v>
+        <v>0.399985111</v>
       </c>
       <c r="Y8">
         <v>0</v>
@@ -12112,10 +12112,10 @@
         <v>0</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>0.55505099400000002</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>4.4963894999999997E-2</v>
       </c>
       <c r="AJ8">
         <v>0</v>
@@ -12243,7 +12243,7 @@
         <v>0</v>
       </c>
       <c r="X9">
-        <v>0.75435141900000002</v>
+        <v>0.41594354500000003</v>
       </c>
       <c r="Y9">
         <v>0</v>
@@ -12273,10 +12273,10 @@
         <v>0.245648581</v>
       </c>
       <c r="AH9">
-        <v>0</v>
+        <v>0.33246167500000001</v>
       </c>
       <c r="AI9">
-        <v>0</v>
+        <v>5.9461990000000001E-3</v>
       </c>
       <c r="AJ9">
         <v>0</v>
@@ -12404,7 +12404,7 @@
         <v>0</v>
       </c>
       <c r="X10">
-        <v>0.75435141900000002</v>
+        <v>0.39439856499999998</v>
       </c>
       <c r="Y10">
         <v>0</v>
@@ -12434,10 +12434,10 @@
         <v>0.245648581</v>
       </c>
       <c r="AH10">
-        <v>0</v>
+        <v>0.34557880800000002</v>
       </c>
       <c r="AI10">
-        <v>0</v>
+        <v>1.4374046E-2</v>
       </c>
       <c r="AJ10">
         <v>0</v>
@@ -12734,7 +12734,7 @@
         <v>0</v>
       </c>
       <c r="Y14">
-        <v>0.55028127100000002</v>
+        <v>0.25957514999999998</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -12761,10 +12761,10 @@
         <v>0.44971872899999998</v>
       </c>
       <c r="AH14">
-        <v>0</v>
+        <v>0.28309632800000001</v>
       </c>
       <c r="AI14">
-        <v>0</v>
+        <v>7.6097930000000001E-3</v>
       </c>
       <c r="AJ14">
         <v>0</v>
@@ -12895,7 +12895,7 @@
         <v>0</v>
       </c>
       <c r="Y15">
-        <v>0.73624568700000004</v>
+        <v>0.347194577</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -12922,10 +12922,10 @@
         <v>0.26375431300000002</v>
       </c>
       <c r="AH15">
-        <v>0</v>
+        <v>0.37896261199999998</v>
       </c>
       <c r="AI15">
-        <v>0</v>
+        <v>1.0088498E-2</v>
       </c>
       <c r="AJ15">
         <v>0</v>
@@ -13214,7 +13214,7 @@
         <v>0</v>
       </c>
       <c r="X17">
-        <v>1</v>
+        <v>0.399985111</v>
       </c>
       <c r="Y17">
         <v>0</v>
@@ -13244,10 +13244,10 @@
         <v>0</v>
       </c>
       <c r="AH17">
-        <v>0</v>
+        <v>0.55505099400000002</v>
       </c>
       <c r="AI17">
-        <v>0</v>
+        <v>4.4963894999999997E-2</v>
       </c>
       <c r="AJ17">
         <v>0</v>
@@ -13375,7 +13375,7 @@
         <v>0</v>
       </c>
       <c r="X18">
-        <v>0.75435141900000002</v>
+        <v>0.41594354500000003</v>
       </c>
       <c r="Y18">
         <v>0</v>
@@ -13405,10 +13405,10 @@
         <v>0.245648581</v>
       </c>
       <c r="AH18">
-        <v>0</v>
+        <v>0.33246167500000001</v>
       </c>
       <c r="AI18">
-        <v>0</v>
+        <v>5.9461990000000001E-3</v>
       </c>
       <c r="AJ18">
         <v>0</v>
@@ -13536,7 +13536,7 @@
         <v>0</v>
       </c>
       <c r="X19">
-        <v>0.75435141900000002</v>
+        <v>0.39439856499999998</v>
       </c>
       <c r="Y19">
         <v>0</v>
@@ -13566,10 +13566,10 @@
         <v>0.245648581</v>
       </c>
       <c r="AH19">
-        <v>0</v>
+        <v>0.34557880800000002</v>
       </c>
       <c r="AI19">
-        <v>0</v>
+        <v>1.4374046E-2</v>
       </c>
       <c r="AJ19">
         <v>0</v>
@@ -13866,7 +13866,7 @@
         <v>0</v>
       </c>
       <c r="Y23">
-        <v>0.70398750300000001</v>
+        <v>0.480142966</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -13893,10 +13893,10 @@
         <v>0.29601249699999999</v>
       </c>
       <c r="AH23">
-        <v>0</v>
+        <v>0.210068117</v>
       </c>
       <c r="AI23">
-        <v>0</v>
+        <v>1.3776419E-2</v>
       </c>
       <c r="AJ23">
         <v>0</v>
@@ -14027,7 +14027,7 @@
         <v>0</v>
       </c>
       <c r="Y24">
-        <v>0.57983010999999995</v>
+        <v>0.39823637499999998</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -14054,10 +14054,10 @@
         <v>0.42016988999999999</v>
       </c>
       <c r="AH24">
-        <v>0</v>
+        <v>0.170194022</v>
       </c>
       <c r="AI24">
-        <v>0</v>
+        <v>1.1399713000000001E-2</v>
       </c>
       <c r="AJ24">
         <v>0</v>
@@ -14346,7 +14346,7 @@
         <v>0</v>
       </c>
       <c r="X26">
-        <v>0.407668947</v>
+        <v>0.28238603800000001</v>
       </c>
       <c r="Y26">
         <v>0</v>
@@ -14376,10 +14376,10 @@
         <v>0.592331053</v>
       </c>
       <c r="AH26">
-        <v>0</v>
+        <v>9.1251813000000001E-2</v>
       </c>
       <c r="AI26">
-        <v>0</v>
+        <v>3.4031095999999997E-2</v>
       </c>
       <c r="AJ26">
         <v>0</v>
@@ -14507,7 +14507,7 @@
         <v>0</v>
       </c>
       <c r="X27">
-        <v>0.75439887000000005</v>
+        <v>0.51313159200000003</v>
       </c>
       <c r="Y27">
         <v>0</v>
@@ -14534,13 +14534,13 @@
         <v>0</v>
       </c>
       <c r="AG27">
-        <v>0.24560113</v>
+        <v>0.245601131</v>
       </c>
       <c r="AH27">
-        <v>0</v>
+        <v>0.227081377</v>
       </c>
       <c r="AI27">
-        <v>0</v>
+        <v>1.41859E-2</v>
       </c>
       <c r="AJ27">
         <v>0</v>
@@ -14668,7 +14668,7 @@
         <v>0</v>
       </c>
       <c r="X28">
-        <v>0.75439887000000005</v>
+        <v>0.51142569199999999</v>
       </c>
       <c r="Y28">
         <v>0</v>
@@ -14695,13 +14695,13 @@
         <v>0</v>
       </c>
       <c r="AG28">
-        <v>0.24560113</v>
+        <v>0.245601131</v>
       </c>
       <c r="AH28">
-        <v>0</v>
+        <v>0.23490525200000001</v>
       </c>
       <c r="AI28">
-        <v>0</v>
+        <v>8.0679259999999996E-3</v>
       </c>
       <c r="AJ28">
         <v>0</v>
@@ -17841,24 +17841,24 @@
         <v>412</v>
       </c>
     </row>
-    <row r="56" spans="1:28" ht="45" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:28" ht="60" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
         <v>413</v>
       </c>
       <c r="B56" s="13">
-        <f>INDEX('EPS Inputs'!$B$5:$BA$5,MATCH("ISIC 28",'EPS Inputs'!$B$4:$BA$4,0))</f>
+        <f>1-INDEX('EPS Inputs'!$B$5:$BA$5,MATCH("ISIC 41T43",'EPS Inputs'!$B$4:$BA$4,0))</f>
         <v>0.55028127100000002</v>
       </c>
       <c r="C56" s="13">
-        <f>INDEX('EPS Inputs'!$B$6:$BA$6,MATCH("ISIC 28",'EPS Inputs'!$B$4:$BA$4,0))</f>
+        <f>1-INDEX('EPS Inputs'!$B$6:$BA$6,MATCH("ISIC 41T43",'EPS Inputs'!$B$4:$BA$4,0))</f>
         <v>0.73624568700000004</v>
       </c>
       <c r="D56" s="13">
-        <f>INDEX('EPS Inputs'!$B$14:$BA$14,MATCH("ISIC 28",'EPS Inputs'!$B$13:$BA$13,0))</f>
+        <f>1-INDEX('EPS Inputs'!$B$14:$BA$14,MATCH("ISIC 41T43",'EPS Inputs'!$B$13:$BA$13,0))</f>
         <v>0.55028127100000002</v>
       </c>
       <c r="E56" s="13">
-        <f>INDEX('EPS Inputs'!$B$15:$BA$15,MATCH("ISIC 28",'EPS Inputs'!$B$13:$BA$13,0))</f>
+        <f>1-INDEX('EPS Inputs'!$B$15:$BA$15,MATCH("ISIC 41T43",'EPS Inputs'!$B$13:$BA$13,0))</f>
         <v>0.73624568700000004</v>
       </c>
       <c r="F56" t="s">
@@ -19450,7 +19450,7 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <f t="shared" ref="C2:C19" si="0">IF(AND(ABS(B2-1)&gt;0.000000001,ABS(B2)&gt;0.000000001),1,0)</f>
+        <f t="shared" ref="C2:C19" si="0">IF(AND(ABS(B2-1)&gt;0.00000001,ABS(B2)&gt;0.00000001),1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -19642,7 +19642,7 @@
       </c>
       <c r="B17">
         <f>SUM('SoBRCbIC-commercial'!B5:BA5)</f>
-        <v>1</v>
+        <v>0.99999999999999989</v>
       </c>
       <c r="C17">
         <f t="shared" si="0"/>
@@ -19668,7 +19668,7 @@
       </c>
       <c r="B19">
         <f>SUM('SoBRCbIC-commercial'!B7:BA7)</f>
-        <v>1</v>
+        <v>1.0000000010000001</v>
       </c>
       <c r="C19">
         <f t="shared" si="0"/>
@@ -19680,8 +19680,8 @@
         <v>437</v>
       </c>
       <c r="B20">
-        <f>INDEX('EPS Inputs'!$B$5:$BA$5,MATCH("ISIC 28",'EPS Inputs'!$B$4:$BA$4,0))+INDEX('EPS Inputs'!$B$5:$BA$5,MATCH("ISIC 41T43",'EPS Inputs'!$B$4:$BA$4,0))</f>
-        <v>1</v>
+        <f>INDEX('EPS Inputs'!$B$5:$BA$5,MATCH("ISIC 28",'EPS Inputs'!$B$4:$BA$4,0))+INDEX('EPS Inputs'!$B$5:$BA$5,MATCH("ISIC 41T43",'EPS Inputs'!$B$4:$BA$4,0))+INDEX('EPS Inputs'!$B$5:$BA$5,MATCH("ISIC 45T47",'EPS Inputs'!$B$4:$BA$4,0))+INDEX('EPS Inputs'!$B$5:$BA$5,MATCH("ISIC 49",'EPS Inputs'!$B$4:$BA$4,0))</f>
+        <v>0.99999999999999989</v>
       </c>
       <c r="C20">
         <f t="shared" ref="C20:C25" si="1">IF(ABS(B20-1)&gt;0.000000001,1,0)</f>
@@ -19693,7 +19693,7 @@
         <v>438</v>
       </c>
       <c r="B21">
-        <f>INDEX('EPS Inputs'!$B$6:$BA$6,MATCH("ISIC 28",'EPS Inputs'!$B$4:$BA$4,0))+INDEX('EPS Inputs'!$B$6:$BA$6,MATCH("ISIC 41T43",'EPS Inputs'!$B$4:$BA$4,0))</f>
+        <f>INDEX('EPS Inputs'!$B$6:$BA$6,MATCH("ISIC 28",'EPS Inputs'!$B$4:$BA$4,0))+INDEX('EPS Inputs'!$B$6:$BA$6,MATCH("ISIC 41T43",'EPS Inputs'!$B$4:$BA$4,0))+INDEX('EPS Inputs'!$B$6:$BA$6,MATCH("ISIC 45T47",'EPS Inputs'!$B$4:$BA$4,0))+INDEX('EPS Inputs'!$B$6:$BA$6,MATCH("ISIC 49",'EPS Inputs'!$B$4:$BA$4,0))</f>
         <v>1</v>
       </c>
       <c r="C21">
@@ -19706,8 +19706,8 @@
         <v>439</v>
       </c>
       <c r="B22">
-        <f>INDEX('EPS Inputs'!$B$14:$BA$14,MATCH("ISIC 28",'EPS Inputs'!$B$13:$BA$13,0))+INDEX('EPS Inputs'!$B$14:$BA$14,MATCH("ISIC 41T43",'EPS Inputs'!$B$13:$BA$13,0))</f>
-        <v>1</v>
+        <f>INDEX('EPS Inputs'!$B$14:$BA$14,MATCH("ISIC 28",'EPS Inputs'!$B$13:$BA$13,0))+INDEX('EPS Inputs'!$B$14:$BA$14,MATCH("ISIC 41T43",'EPS Inputs'!$B$13:$BA$13,0))+INDEX('EPS Inputs'!$B$14:$BA$14,MATCH("ISIC 45T47",'EPS Inputs'!$B$13:$BA$13,0))+INDEX('EPS Inputs'!$B$14:$BA$14,MATCH("ISIC 49",'EPS Inputs'!$B$13:$BA$13,0))</f>
+        <v>0.99999999999999989</v>
       </c>
       <c r="C22">
         <f t="shared" si="1"/>
@@ -19719,7 +19719,7 @@
         <v>440</v>
       </c>
       <c r="B23">
-        <f>INDEX('EPS Inputs'!$B$15:$BA$15,MATCH("ISIC 28",'EPS Inputs'!$B$13:$BA$13,0))+INDEX('EPS Inputs'!$B$15:$BA$15,MATCH("ISIC 41T43",'EPS Inputs'!$B$13:$BA$13,0))</f>
+        <f>INDEX('EPS Inputs'!$B$15:$BA$15,MATCH("ISIC 28",'EPS Inputs'!$B$13:$BA$13,0))+INDEX('EPS Inputs'!$B$15:$BA$15,MATCH("ISIC 41T43",'EPS Inputs'!$B$13:$BA$13,0))+INDEX('EPS Inputs'!$B$15:$BA$15,MATCH("ISIC 45T47",'EPS Inputs'!$B$13:$BA$13,0))+INDEX('EPS Inputs'!$B$15:$BA$15,MATCH("ISIC 49",'EPS Inputs'!$B$13:$BA$13,0))</f>
         <v>1</v>
       </c>
       <c r="C23">
